--- a/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G4/G4_T1936_W0015F0003T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>62.42591795704853</v>
+        <v>10.14421166802039</v>
       </c>
       <c r="D2" t="n">
-        <v>38.3721203360449</v>
+        <v>6.235469554607296</v>
       </c>
       <c r="E2" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F2" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>71.68295424082497</v>
+        <v>11.64848006413406</v>
       </c>
       <c r="D3" t="n">
-        <v>53.28765561150313</v>
+        <v>8.659244036869259</v>
       </c>
       <c r="E3" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F3" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>50.21059268726292</v>
+        <v>8.159221311680223</v>
       </c>
       <c r="D4" t="n">
-        <v>22.96825107653857</v>
+        <v>3.732340799937518</v>
       </c>
       <c r="E4" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F4" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>55.99273799378587</v>
+        <v>9.098819923990204</v>
       </c>
       <c r="D5" t="n">
-        <v>54.6405832664645</v>
+        <v>8.879094780800482</v>
       </c>
       <c r="E5" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F5" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -608,16 +608,16 @@
         <v>5</v>
       </c>
       <c r="C6" t="n">
-        <v>16.49956923804591</v>
+        <v>2.681180001182461</v>
       </c>
       <c r="D6" t="n">
-        <v>16.4349057960773</v>
+        <v>2.670672191862561</v>
       </c>
       <c r="E6" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F6" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -640,16 +640,16 @@
         <v>6</v>
       </c>
       <c r="C7" t="n">
-        <v>64.69699542466697</v>
+        <v>10.51326175650838</v>
       </c>
       <c r="D7" t="n">
-        <v>63.03326514415092</v>
+        <v>10.24290558592453</v>
       </c>
       <c r="E7" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F7" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -672,16 +672,16 @@
         <v>7</v>
       </c>
       <c r="C8" t="n">
-        <v>53.2975462406138</v>
+        <v>8.660851264099744</v>
       </c>
       <c r="D8" t="n">
-        <v>55.3081791245239</v>
+        <v>8.987579107735135</v>
       </c>
       <c r="E8" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F8" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -704,16 +704,16 @@
         <v>8</v>
       </c>
       <c r="C9" t="n">
-        <v>51.56765602088192</v>
+        <v>8.379744103393312</v>
       </c>
       <c r="D9" t="n">
-        <v>49.88779133142931</v>
+        <v>8.106766091357263</v>
       </c>
       <c r="E9" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F9" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -736,16 +736,16 @@
         <v>9</v>
       </c>
       <c r="C10" t="n">
-        <v>33.66986292596343</v>
+        <v>5.471352725469058</v>
       </c>
       <c r="D10" t="n">
-        <v>35.05950475054547</v>
+        <v>5.697169521963639</v>
       </c>
       <c r="E10" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F10" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -768,16 +768,16 @@
         <v>10</v>
       </c>
       <c r="C11" t="n">
-        <v>49.32094520593853</v>
+        <v>8.014653595965012</v>
       </c>
       <c r="D11" t="n">
-        <v>50.64721394361266</v>
+        <v>8.230172265837057</v>
       </c>
       <c r="E11" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F11" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -800,16 +800,16 @@
         <v>11</v>
       </c>
       <c r="C12" t="n">
-        <v>53.93530797238153</v>
+        <v>8.764487545511999</v>
       </c>
       <c r="D12" t="n">
-        <v>54.42903011565181</v>
+        <v>8.844717393793418</v>
       </c>
       <c r="E12" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F12" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -832,16 +832,16 @@
         <v>12</v>
       </c>
       <c r="C13" t="n">
-        <v>57.98526773385457</v>
+        <v>9.422606006751368</v>
       </c>
       <c r="D13" t="n">
-        <v>57.99459740808564</v>
+        <v>9.424122078813916</v>
       </c>
       <c r="E13" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F13" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -864,16 +864,16 @@
         <v>13</v>
       </c>
       <c r="C14" t="n">
-        <v>41.53418412924509</v>
+        <v>6.749304921002327</v>
       </c>
       <c r="D14" t="n">
-        <v>40.97584473608037</v>
+        <v>6.65857476961306</v>
       </c>
       <c r="E14" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F14" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -896,16 +896,16 @@
         <v>14</v>
       </c>
       <c r="C15" t="n">
-        <v>25.2792656613724</v>
+        <v>4.107880669973015</v>
       </c>
       <c r="D15" t="n">
-        <v>25.50785271645677</v>
+        <v>4.145026066424226</v>
       </c>
       <c r="E15" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F15" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -928,16 +928,16 @@
         <v>15</v>
       </c>
       <c r="C16" t="n">
-        <v>30.49616253108719</v>
+        <v>4.955626411301669</v>
       </c>
       <c r="D16" t="n">
-        <v>30.00672769330367</v>
+        <v>4.876093250161846</v>
       </c>
       <c r="E16" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F16" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -960,16 +960,16 @@
         <v>16</v>
       </c>
       <c r="C17" t="n">
-        <v>8.599144560191704</v>
+        <v>1.397360991031152</v>
       </c>
       <c r="D17" t="n">
-        <v>8.711910906836433</v>
+        <v>1.41568552236092</v>
       </c>
       <c r="E17" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F17" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -992,16 +992,16 @@
         <v>17</v>
       </c>
       <c r="C18" t="n">
-        <v>46.56392660625733</v>
+        <v>7.566638073516816</v>
       </c>
       <c r="D18" t="n">
-        <v>45.46911000307771</v>
+        <v>7.388730375500128</v>
       </c>
       <c r="E18" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F18" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1024,16 +1024,16 @@
         <v>18</v>
       </c>
       <c r="C19" t="n">
-        <v>35.21733435980454</v>
+        <v>5.722816833468237</v>
       </c>
       <c r="D19" t="n">
-        <v>34.02781922837445</v>
+        <v>5.529520624610848</v>
       </c>
       <c r="E19" t="n">
-        <v>16.50884136618382</v>
+        <v>2.68268672200487</v>
       </c>
       <c r="F19" t="n">
-        <v>15.11276074424389</v>
+        <v>2.455823620939633</v>
       </c>
       <c r="G19" t="inlineStr">
         <is>
